--- a/idecba/masa_salarial.xlsx
+++ b/idecba/masa_salarial.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\INDUSTRIA\INDICADORES LABORALES INDUSTRIALES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\INDUSTRIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25455" windowHeight="8745"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
   </bookViews>
   <sheets>
     <sheet name="ee_industria_masa_salarial" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="58">
   <si>
     <t xml:space="preserve">Año </t>
   </si>
@@ -225,10 +225,10 @@
     <t>2025*</t>
   </si>
   <si>
-    <t>Masa salarial por rama de actividad (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Marzo 2026</t>
+    <t>2026*</t>
   </si>
   <si>
-    <t>2026*</t>
+    <t>Masa salarial por rama de actividad (Índice base octubre 2001 = 100). Ciudad de Buenos Aires. Octubre 2001/Junio 2026</t>
   </si>
 </sst>
 </file>
@@ -1412,38 +1412,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1456,6 +1435,27 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="45" xfId="35" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1813,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CD300"/>
+  <dimension ref="A1:CD303"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="7" customWidth="1"/>
@@ -1822,44 +1822,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
+      <c r="A1" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="76"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="84"/>
-      <c r="B3" s="86"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1892,7 +1892,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="77">
+      <c r="A4" s="80">
         <v>2001</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1930,7 +1930,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="74"/>
       <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
@@ -1966,7 +1966,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="10" t="s">
         <v>15</v>
       </c>
@@ -2002,7 +2002,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="72">
+      <c r="A7" s="74">
         <v>2002</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2040,7 +2040,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
@@ -2076,7 +2076,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="74"/>
       <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
@@ -2112,7 +2112,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="9" t="s">
         <v>19</v>
       </c>
@@ -2148,7 +2148,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="74"/>
       <c r="B11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2184,7 +2184,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2220,7 +2220,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="74"/>
       <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
@@ -2256,7 +2256,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="9" t="s">
         <v>23</v>
       </c>
@@ -2292,7 +2292,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="9" t="s">
         <v>24</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="9" t="s">
         <v>13</v>
       </c>
@@ -2364,7 +2364,7 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="72"/>
+      <c r="A17" s="74"/>
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -2400,7 +2400,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
+      <c r="A18" s="75"/>
       <c r="B18" s="10" t="s">
         <v>15</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="72">
+      <c r="A19" s="74">
         <v>2003</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -2474,7 +2474,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="72"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="9" t="s">
         <v>17</v>
       </c>
@@ -2510,7 +2510,7 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="72"/>
+      <c r="A21" s="74"/>
       <c r="B21" s="9" t="s">
         <v>18</v>
       </c>
@@ -2546,7 +2546,7 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="72"/>
+      <c r="A22" s="74"/>
       <c r="B22" s="9" t="s">
         <v>19</v>
       </c>
@@ -2582,7 +2582,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="72"/>
+      <c r="A23" s="74"/>
       <c r="B23" s="9" t="s">
         <v>20</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
+      <c r="A24" s="74"/>
       <c r="B24" s="9" t="s">
         <v>21</v>
       </c>
@@ -2654,7 +2654,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="72"/>
+      <c r="A25" s="74"/>
       <c r="B25" s="9" t="s">
         <v>22</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="72"/>
+      <c r="A26" s="74"/>
       <c r="B26" s="9" t="s">
         <v>23</v>
       </c>
@@ -2726,7 +2726,7 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
+      <c r="A27" s="74"/>
       <c r="B27" s="9" t="s">
         <v>24</v>
       </c>
@@ -2762,7 +2762,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="72"/>
+      <c r="A28" s="74"/>
       <c r="B28" s="9" t="s">
         <v>13</v>
       </c>
@@ -2798,7 +2798,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="72"/>
+      <c r="A29" s="74"/>
       <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="10" t="s">
         <v>15</v>
       </c>
@@ -2870,7 +2870,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="72">
+      <c r="A31" s="74">
         <v>2004</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -2908,7 +2908,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="72"/>
+      <c r="A32" s="74"/>
       <c r="B32" s="9" t="s">
         <v>17</v>
       </c>
@@ -2944,7 +2944,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="72"/>
+      <c r="A33" s="74"/>
       <c r="B33" s="9" t="s">
         <v>18</v>
       </c>
@@ -2980,7 +2980,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="72"/>
+      <c r="A34" s="74"/>
       <c r="B34" s="9" t="s">
         <v>19</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="72"/>
+      <c r="A35" s="74"/>
       <c r="B35" s="9" t="s">
         <v>20</v>
       </c>
@@ -3052,7 +3052,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="72"/>
+      <c r="A36" s="74"/>
       <c r="B36" s="9" t="s">
         <v>21</v>
       </c>
@@ -3088,7 +3088,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="72"/>
+      <c r="A37" s="74"/>
       <c r="B37" s="9" t="s">
         <v>22</v>
       </c>
@@ -3124,7 +3124,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="72"/>
+      <c r="A38" s="74"/>
       <c r="B38" s="9" t="s">
         <v>23</v>
       </c>
@@ -3160,7 +3160,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="72"/>
+      <c r="A39" s="74"/>
       <c r="B39" s="9" t="s">
         <v>24</v>
       </c>
@@ -3196,7 +3196,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="72"/>
+      <c r="A40" s="74"/>
       <c r="B40" s="9" t="s">
         <v>13</v>
       </c>
@@ -3232,7 +3232,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="72"/>
+      <c r="A41" s="74"/>
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
@@ -3268,7 +3268,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
+      <c r="A42" s="75"/>
       <c r="B42" s="10" t="s">
         <v>15</v>
       </c>
@@ -3304,7 +3304,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="72">
+      <c r="A43" s="74">
         <v>2005</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -3342,7 +3342,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="72"/>
+      <c r="A44" s="74"/>
       <c r="B44" s="9" t="s">
         <v>17</v>
       </c>
@@ -3378,7 +3378,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="72"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="9" t="s">
         <v>18</v>
       </c>
@@ -3414,7 +3414,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="72"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="9" t="s">
         <v>19</v>
       </c>
@@ -3450,7 +3450,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="72"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="9" t="s">
         <v>20</v>
       </c>
@@ -3486,7 +3486,7 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="72"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="9" t="s">
         <v>21</v>
       </c>
@@ -3522,7 +3522,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="72"/>
+      <c r="A49" s="74"/>
       <c r="B49" s="9" t="s">
         <v>22</v>
       </c>
@@ -3558,7 +3558,7 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="72"/>
+      <c r="A50" s="74"/>
       <c r="B50" s="9" t="s">
         <v>23</v>
       </c>
@@ -3594,7 +3594,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
+      <c r="A51" s="74"/>
       <c r="B51" s="9" t="s">
         <v>24</v>
       </c>
@@ -3630,7 +3630,7 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="72"/>
+      <c r="A52" s="74"/>
       <c r="B52" s="9" t="s">
         <v>13</v>
       </c>
@@ -3666,7 +3666,7 @@
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="74"/>
       <c r="B53" s="9" t="s">
         <v>14</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="73"/>
+      <c r="A54" s="75"/>
       <c r="B54" s="10" t="s">
         <v>15</v>
       </c>
@@ -3738,7 +3738,7 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="72">
+      <c r="A55" s="74">
         <v>2006</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -3776,7 +3776,7 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="72"/>
+      <c r="A56" s="74"/>
       <c r="B56" s="9" t="s">
         <v>17</v>
       </c>
@@ -3812,7 +3812,7 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="72"/>
+      <c r="A57" s="74"/>
       <c r="B57" s="9" t="s">
         <v>18</v>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
+      <c r="A58" s="74"/>
       <c r="B58" s="9" t="s">
         <v>19</v>
       </c>
@@ -3884,7 +3884,7 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
+      <c r="A59" s="74"/>
       <c r="B59" s="9" t="s">
         <v>20</v>
       </c>
@@ -3920,7 +3920,7 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
+      <c r="A60" s="74"/>
       <c r="B60" s="9" t="s">
         <v>21</v>
       </c>
@@ -3956,7 +3956,7 @@
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
+      <c r="A61" s="74"/>
       <c r="B61" s="9" t="s">
         <v>22</v>
       </c>
@@ -3992,7 +3992,7 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
+      <c r="A62" s="74"/>
       <c r="B62" s="9" t="s">
         <v>23</v>
       </c>
@@ -4028,7 +4028,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
+      <c r="A63" s="74"/>
       <c r="B63" s="9" t="s">
         <v>24</v>
       </c>
@@ -4064,7 +4064,7 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="72"/>
+      <c r="A64" s="74"/>
       <c r="B64" s="9" t="s">
         <v>13</v>
       </c>
@@ -4100,7 +4100,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
+      <c r="A65" s="74"/>
       <c r="B65" s="9" t="s">
         <v>14</v>
       </c>
@@ -4136,7 +4136,7 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="73"/>
+      <c r="A66" s="75"/>
       <c r="B66" s="10" t="s">
         <v>15</v>
       </c>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="72">
+      <c r="A67" s="74">
         <v>2007</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -4210,7 +4210,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="72"/>
+      <c r="A68" s="74"/>
       <c r="B68" s="9" t="s">
         <v>17</v>
       </c>
@@ -4246,7 +4246,7 @@
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
+      <c r="A69" s="74"/>
       <c r="B69" s="9" t="s">
         <v>18</v>
       </c>
@@ -4282,7 +4282,7 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="72"/>
+      <c r="A70" s="74"/>
       <c r="B70" s="9" t="s">
         <v>19</v>
       </c>
@@ -4318,7 +4318,7 @@
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="9" t="s">
         <v>20</v>
       </c>
@@ -4354,7 +4354,7 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
+      <c r="A72" s="74"/>
       <c r="B72" s="9" t="s">
         <v>21</v>
       </c>
@@ -4390,7 +4390,7 @@
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
+      <c r="A73" s="74"/>
       <c r="B73" s="9" t="s">
         <v>22</v>
       </c>
@@ -4426,7 +4426,7 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
+      <c r="A74" s="74"/>
       <c r="B74" s="9" t="s">
         <v>23</v>
       </c>
@@ -4462,7 +4462,7 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
+      <c r="A75" s="74"/>
       <c r="B75" s="9" t="s">
         <v>24</v>
       </c>
@@ -4498,7 +4498,7 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
+      <c r="A76" s="74"/>
       <c r="B76" s="9" t="s">
         <v>13</v>
       </c>
@@ -4534,7 +4534,7 @@
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
+      <c r="A77" s="74"/>
       <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
@@ -4570,7 +4570,7 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="73"/>
+      <c r="A78" s="75"/>
       <c r="B78" s="10" t="s">
         <v>15</v>
       </c>
@@ -4606,7 +4606,7 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="72">
+      <c r="A79" s="74">
         <v>2008</v>
       </c>
       <c r="B79" s="9" t="s">
@@ -4644,7 +4644,7 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
+      <c r="A80" s="74"/>
       <c r="B80" s="9" t="s">
         <v>17</v>
       </c>
@@ -4680,7 +4680,7 @@
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="72"/>
+      <c r="A81" s="74"/>
       <c r="B81" s="9" t="s">
         <v>18</v>
       </c>
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="72"/>
+      <c r="A82" s="74"/>
       <c r="B82" s="9" t="s">
         <v>19</v>
       </c>
@@ -4752,7 +4752,7 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
+      <c r="A83" s="74"/>
       <c r="B83" s="9" t="s">
         <v>20</v>
       </c>
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
+      <c r="A84" s="74"/>
       <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
@@ -4824,7 +4824,7 @@
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
+      <c r="A85" s="74"/>
       <c r="B85" s="9" t="s">
         <v>22</v>
       </c>
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
+      <c r="A86" s="74"/>
       <c r="B86" s="9" t="s">
         <v>23</v>
       </c>
@@ -4896,7 +4896,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
+      <c r="A87" s="74"/>
       <c r="B87" s="9" t="s">
         <v>24</v>
       </c>
@@ -4932,7 +4932,7 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="72"/>
+      <c r="A88" s="74"/>
       <c r="B88" s="9" t="s">
         <v>13</v>
       </c>
@@ -4968,7 +4968,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="72"/>
+      <c r="A89" s="74"/>
       <c r="B89" s="9" t="s">
         <v>14</v>
       </c>
@@ -5004,7 +5004,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="73"/>
+      <c r="A90" s="75"/>
       <c r="B90" s="10" t="s">
         <v>15</v>
       </c>
@@ -5040,7 +5040,7 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="77">
+      <c r="A91" s="80">
         <v>2009</v>
       </c>
       <c r="B91" s="9" t="s">
@@ -5078,7 +5078,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="72"/>
+      <c r="A92" s="74"/>
       <c r="B92" s="9" t="s">
         <v>17</v>
       </c>
@@ -5114,7 +5114,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="72"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="9" t="s">
         <v>18</v>
       </c>
@@ -5150,7 +5150,7 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="9" t="s">
         <v>19</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="72"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="9" t="s">
         <v>20</v>
       </c>
@@ -5222,7 +5222,7 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="72"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="9" t="s">
         <v>21</v>
       </c>
@@ -5258,7 +5258,7 @@
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="72"/>
+      <c r="A97" s="74"/>
       <c r="B97" s="9" t="s">
         <v>22</v>
       </c>
@@ -5294,7 +5294,7 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="72"/>
+      <c r="A98" s="74"/>
       <c r="B98" s="9" t="s">
         <v>23</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="72"/>
+      <c r="A99" s="74"/>
       <c r="B99" s="9" t="s">
         <v>24</v>
       </c>
@@ -5366,7 +5366,7 @@
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="72"/>
+      <c r="A100" s="74"/>
       <c r="B100" s="9" t="s">
         <v>13</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="72"/>
+      <c r="A101" s="74"/>
       <c r="B101" s="9" t="s">
         <v>14</v>
       </c>
@@ -5438,7 +5438,7 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="73"/>
+      <c r="A102" s="75"/>
       <c r="B102" s="10" t="s">
         <v>15</v>
       </c>
@@ -5474,7 +5474,7 @@
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="77">
+      <c r="A103" s="80">
         <v>2010</v>
       </c>
       <c r="B103" s="9" t="s">
@@ -5512,7 +5512,7 @@
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="72"/>
+      <c r="A104" s="74"/>
       <c r="B104" s="9" t="s">
         <v>17</v>
       </c>
@@ -5548,7 +5548,7 @@
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="72"/>
+      <c r="A105" s="74"/>
       <c r="B105" s="9" t="s">
         <v>18</v>
       </c>
@@ -5584,7 +5584,7 @@
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="72"/>
+      <c r="A106" s="74"/>
       <c r="B106" s="9" t="s">
         <v>19</v>
       </c>
@@ -5620,7 +5620,7 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="72"/>
+      <c r="A107" s="74"/>
       <c r="B107" s="9" t="s">
         <v>20</v>
       </c>
@@ -5656,7 +5656,7 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="72"/>
+      <c r="A108" s="74"/>
       <c r="B108" s="9" t="s">
         <v>21</v>
       </c>
@@ -5692,7 +5692,7 @@
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="72"/>
+      <c r="A109" s="74"/>
       <c r="B109" s="9" t="s">
         <v>22</v>
       </c>
@@ -5728,7 +5728,7 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="72"/>
+      <c r="A110" s="74"/>
       <c r="B110" s="9" t="s">
         <v>23</v>
       </c>
@@ -5764,7 +5764,7 @@
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="72"/>
+      <c r="A111" s="74"/>
       <c r="B111" s="9" t="s">
         <v>24</v>
       </c>
@@ -5800,7 +5800,7 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="72"/>
+      <c r="A112" s="74"/>
       <c r="B112" s="9" t="s">
         <v>13</v>
       </c>
@@ -5836,7 +5836,7 @@
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="72"/>
+      <c r="A113" s="74"/>
       <c r="B113" s="9" t="s">
         <v>14</v>
       </c>
@@ -5872,7 +5872,7 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="73"/>
+      <c r="A114" s="75"/>
       <c r="B114" s="10" t="s">
         <v>15</v>
       </c>
@@ -5908,7 +5908,7 @@
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="77">
+      <c r="A115" s="80">
         <v>2011</v>
       </c>
       <c r="B115" s="9" t="s">
@@ -5946,7 +5946,7 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="72"/>
+      <c r="A116" s="74"/>
       <c r="B116" s="9" t="s">
         <v>17</v>
       </c>
@@ -5982,7 +5982,7 @@
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="72"/>
+      <c r="A117" s="74"/>
       <c r="B117" s="9" t="s">
         <v>18</v>
       </c>
@@ -6018,7 +6018,7 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="72"/>
+      <c r="A118" s="74"/>
       <c r="B118" s="9" t="s">
         <v>19</v>
       </c>
@@ -6054,7 +6054,7 @@
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="72"/>
+      <c r="A119" s="74"/>
       <c r="B119" s="9" t="s">
         <v>20</v>
       </c>
@@ -6090,7 +6090,7 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="72"/>
+      <c r="A120" s="74"/>
       <c r="B120" s="9" t="s">
         <v>21</v>
       </c>
@@ -6126,7 +6126,7 @@
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="72"/>
+      <c r="A121" s="74"/>
       <c r="B121" s="9" t="s">
         <v>22</v>
       </c>
@@ -6162,7 +6162,7 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="72"/>
+      <c r="A122" s="74"/>
       <c r="B122" s="9" t="s">
         <v>23</v>
       </c>
@@ -6198,7 +6198,7 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="72"/>
+      <c r="A123" s="74"/>
       <c r="B123" s="9" t="s">
         <v>24</v>
       </c>
@@ -6234,7 +6234,7 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="72"/>
+      <c r="A124" s="74"/>
       <c r="B124" s="9" t="s">
         <v>13</v>
       </c>
@@ -6270,7 +6270,7 @@
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="72"/>
+      <c r="A125" s="74"/>
       <c r="B125" s="9" t="s">
         <v>14</v>
       </c>
@@ -6306,7 +6306,7 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="73"/>
+      <c r="A126" s="75"/>
       <c r="B126" s="10" t="s">
         <v>15</v>
       </c>
@@ -6342,7 +6342,7 @@
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="77">
+      <c r="A127" s="80">
         <v>2012</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -6380,7 +6380,7 @@
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="72"/>
+      <c r="A128" s="74"/>
       <c r="B128" s="9" t="s">
         <v>17</v>
       </c>
@@ -6416,7 +6416,7 @@
       </c>
     </row>
     <row r="129" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A129" s="72"/>
+      <c r="A129" s="74"/>
       <c r="B129" s="9" t="s">
         <v>18</v>
       </c>
@@ -6452,7 +6452,7 @@
       </c>
     </row>
     <row r="130" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A130" s="72"/>
+      <c r="A130" s="74"/>
       <c r="B130" s="9" t="s">
         <v>19</v>
       </c>
@@ -6488,7 +6488,7 @@
       </c>
     </row>
     <row r="131" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A131" s="72"/>
+      <c r="A131" s="74"/>
       <c r="B131" s="9" t="s">
         <v>20</v>
       </c>
@@ -6524,7 +6524,7 @@
       </c>
     </row>
     <row r="132" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A132" s="72"/>
+      <c r="A132" s="74"/>
       <c r="B132" s="9" t="s">
         <v>21</v>
       </c>
@@ -6560,7 +6560,7 @@
       </c>
     </row>
     <row r="133" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A133" s="72"/>
+      <c r="A133" s="74"/>
       <c r="B133" s="9" t="s">
         <v>22</v>
       </c>
@@ -6596,7 +6596,7 @@
       </c>
     </row>
     <row r="134" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A134" s="72"/>
+      <c r="A134" s="74"/>
       <c r="B134" s="9" t="s">
         <v>23</v>
       </c>
@@ -6632,7 +6632,7 @@
       </c>
     </row>
     <row r="135" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A135" s="72"/>
+      <c r="A135" s="74"/>
       <c r="B135" s="9" t="s">
         <v>24</v>
       </c>
@@ -6668,7 +6668,7 @@
       </c>
     </row>
     <row r="136" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A136" s="72"/>
+      <c r="A136" s="74"/>
       <c r="B136" s="9" t="s">
         <v>13</v>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
     </row>
     <row r="137" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A137" s="72"/>
+      <c r="A137" s="74"/>
       <c r="B137" s="9" t="s">
         <v>14</v>
       </c>
@@ -6740,7 +6740,7 @@
       </c>
     </row>
     <row r="138" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A138" s="73"/>
+      <c r="A138" s="75"/>
       <c r="B138" s="10" t="s">
         <v>15</v>
       </c>
@@ -6776,7 +6776,7 @@
       </c>
     </row>
     <row r="139" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A139" s="77">
+      <c r="A139" s="80">
         <v>2013</v>
       </c>
       <c r="B139" s="8" t="s">
@@ -6814,7 +6814,7 @@
       </c>
     </row>
     <row r="140" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A140" s="72"/>
+      <c r="A140" s="74"/>
       <c r="B140" s="9" t="s">
         <v>17</v>
       </c>
@@ -6850,7 +6850,7 @@
       </c>
     </row>
     <row r="141" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A141" s="72"/>
+      <c r="A141" s="74"/>
       <c r="B141" s="9" t="s">
         <v>18</v>
       </c>
@@ -6886,7 +6886,7 @@
       </c>
     </row>
     <row r="142" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A142" s="72"/>
+      <c r="A142" s="74"/>
       <c r="B142" s="9" t="s">
         <v>19</v>
       </c>
@@ -6922,7 +6922,7 @@
       </c>
     </row>
     <row r="143" spans="1:82" x14ac:dyDescent="0.25">
-      <c r="A143" s="72"/>
+      <c r="A143" s="74"/>
       <c r="B143" s="9" t="s">
         <v>20</v>
       </c>
@@ -6958,7 +6958,7 @@
       </c>
     </row>
     <row r="144" spans="1:82" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="72"/>
+      <c r="A144" s="74"/>
       <c r="B144" s="20" t="s">
         <v>21</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="CD144" s="19"/>
     </row>
     <row r="145" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="72"/>
+      <c r="A145" s="74"/>
       <c r="B145" s="9" t="s">
         <v>22</v>
       </c>
@@ -7101,7 +7101,7 @@
       <c r="M145"/>
     </row>
     <row r="146" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="72"/>
+      <c r="A146" s="74"/>
       <c r="B146" s="20" t="s">
         <v>23</v>
       </c>
@@ -7138,7 +7138,7 @@
       <c r="M146"/>
     </row>
     <row r="147" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72"/>
+      <c r="A147" s="74"/>
       <c r="B147" s="20" t="s">
         <v>25</v>
       </c>
@@ -7175,7 +7175,7 @@
       <c r="M147"/>
     </row>
     <row r="148" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="72"/>
+      <c r="A148" s="74"/>
       <c r="B148" s="20" t="s">
         <v>13</v>
       </c>
@@ -7212,7 +7212,7 @@
       <c r="M148"/>
     </row>
     <row r="149" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="72"/>
+      <c r="A149" s="74"/>
       <c r="B149" s="20" t="s">
         <v>14</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="M149"/>
     </row>
     <row r="150" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="73"/>
+      <c r="A150" s="75"/>
       <c r="B150" s="25" t="s">
         <v>15</v>
       </c>
@@ -7286,7 +7286,7 @@
       <c r="M150"/>
     </row>
     <row r="151" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="77">
+      <c r="A151" s="80">
         <v>2014</v>
       </c>
       <c r="B151" s="8" t="s">
@@ -7325,7 +7325,7 @@
       <c r="M151" s="32"/>
     </row>
     <row r="152" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="72"/>
+      <c r="A152" s="74"/>
       <c r="B152" s="9" t="s">
         <v>17</v>
       </c>
@@ -7362,7 +7362,7 @@
       <c r="M152" s="32"/>
     </row>
     <row r="153" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="72"/>
+      <c r="A153" s="74"/>
       <c r="B153" s="9" t="s">
         <v>18</v>
       </c>
@@ -7399,7 +7399,7 @@
       <c r="M153" s="32"/>
     </row>
     <row r="154" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="72"/>
+      <c r="A154" s="74"/>
       <c r="B154" s="9" t="s">
         <v>19</v>
       </c>
@@ -7436,7 +7436,7 @@
       <c r="M154" s="32"/>
     </row>
     <row r="155" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="72"/>
+      <c r="A155" s="74"/>
       <c r="B155" s="9" t="s">
         <v>20</v>
       </c>
@@ -7473,7 +7473,7 @@
       <c r="M155" s="32"/>
     </row>
     <row r="156" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="72"/>
+      <c r="A156" s="74"/>
       <c r="B156" s="9" t="s">
         <v>21</v>
       </c>
@@ -7510,7 +7510,7 @@
       <c r="M156" s="32"/>
     </row>
     <row r="157" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="72"/>
+      <c r="A157" s="74"/>
       <c r="B157" s="9" t="s">
         <v>22</v>
       </c>
@@ -7547,7 +7547,7 @@
       <c r="M157" s="32"/>
     </row>
     <row r="158" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72"/>
+      <c r="A158" s="74"/>
       <c r="B158" s="9" t="s">
         <v>23</v>
       </c>
@@ -7584,7 +7584,7 @@
       <c r="M158" s="32"/>
     </row>
     <row r="159" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="72"/>
+      <c r="A159" s="74"/>
       <c r="B159" s="9" t="s">
         <v>25</v>
       </c>
@@ -7621,7 +7621,7 @@
       <c r="M159" s="32"/>
     </row>
     <row r="160" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="72"/>
+      <c r="A160" s="74"/>
       <c r="B160" s="9" t="s">
         <v>13</v>
       </c>
@@ -7658,7 +7658,7 @@
       <c r="M160" s="32"/>
     </row>
     <row r="161" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="72"/>
+      <c r="A161" s="74"/>
       <c r="B161" s="9" t="s">
         <v>14</v>
       </c>
@@ -7695,7 +7695,7 @@
       <c r="M161" s="32"/>
     </row>
     <row r="162" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="73"/>
+      <c r="A162" s="75"/>
       <c r="B162" s="10" t="s">
         <v>15</v>
       </c>
@@ -7732,7 +7732,7 @@
       <c r="M162" s="32"/>
     </row>
     <row r="163" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="78">
+      <c r="A163" s="84">
         <v>2015</v>
       </c>
       <c r="B163" s="8" t="s">
@@ -7771,7 +7771,7 @@
       <c r="M163" s="32"/>
     </row>
     <row r="164" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="79"/>
+      <c r="A164" s="85"/>
       <c r="B164" s="9" t="s">
         <v>17</v>
       </c>
@@ -7808,7 +7808,7 @@
       <c r="M164" s="32"/>
     </row>
     <row r="165" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="79"/>
+      <c r="A165" s="85"/>
       <c r="B165" s="20" t="s">
         <v>18</v>
       </c>
@@ -7845,7 +7845,7 @@
       <c r="M165" s="32"/>
     </row>
     <row r="166" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="79"/>
+      <c r="A166" s="85"/>
       <c r="B166" s="9" t="s">
         <v>19</v>
       </c>
@@ -7882,7 +7882,7 @@
       <c r="M166" s="32"/>
     </row>
     <row r="167" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="79"/>
+      <c r="A167" s="85"/>
       <c r="B167" s="9" t="s">
         <v>20</v>
       </c>
@@ -7919,7 +7919,7 @@
       <c r="M167" s="32"/>
     </row>
     <row r="168" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="79"/>
+      <c r="A168" s="85"/>
       <c r="B168" s="9" t="s">
         <v>21</v>
       </c>
@@ -7956,7 +7956,7 @@
       <c r="M168" s="32"/>
     </row>
     <row r="169" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="79"/>
+      <c r="A169" s="85"/>
       <c r="B169" s="9" t="s">
         <v>22</v>
       </c>
@@ -7993,7 +7993,7 @@
       <c r="M169" s="32"/>
     </row>
     <row r="170" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="79"/>
+      <c r="A170" s="85"/>
       <c r="B170" s="9" t="s">
         <v>23</v>
       </c>
@@ -8030,7 +8030,7 @@
       <c r="M170" s="32"/>
     </row>
     <row r="171" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="79"/>
+      <c r="A171" s="85"/>
       <c r="B171" s="9" t="s">
         <v>25</v>
       </c>
@@ -8067,7 +8067,7 @@
       <c r="M171" s="32"/>
     </row>
     <row r="172" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="79"/>
+      <c r="A172" s="85"/>
       <c r="B172" s="9" t="s">
         <v>13</v>
       </c>
@@ -8104,7 +8104,7 @@
       <c r="M172" s="32"/>
     </row>
     <row r="173" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="79"/>
+      <c r="A173" s="85"/>
       <c r="B173" s="9" t="s">
         <v>14</v>
       </c>
@@ -8141,7 +8141,7 @@
       <c r="M173" s="32"/>
     </row>
     <row r="174" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="80"/>
+      <c r="A174" s="86"/>
       <c r="B174" s="37" t="s">
         <v>15</v>
       </c>
@@ -12541,7 +12541,7 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B295" s="8" t="s">
         <v>16</v>
@@ -12613,61 +12613,178 @@
         <v>59859.578592527971</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="81"/>
-      <c r="B297" s="68" t="s">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A297" s="70"/>
+      <c r="B297" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C297" s="64">
+      <c r="C297" s="27">
         <v>150395.25533946371</v>
       </c>
-      <c r="D297" s="18">
+      <c r="D297" s="13">
         <v>140677.75010637753</v>
       </c>
-      <c r="E297" s="65">
+      <c r="E297" s="21">
         <v>49135.030650538538</v>
       </c>
-      <c r="F297" s="18">
+      <c r="F297" s="13">
         <v>63207.424018143116</v>
       </c>
-      <c r="G297" s="65">
+      <c r="G297" s="21">
         <v>168845.53419127228</v>
       </c>
-      <c r="H297" s="18">
+      <c r="H297" s="13">
         <v>157960.13333206341</v>
       </c>
-      <c r="I297" s="65">
+      <c r="I297" s="21">
         <v>268817.6165882998</v>
       </c>
-      <c r="J297" s="18">
+      <c r="J297" s="13">
         <v>86904.256273700666</v>
       </c>
-      <c r="K297" s="66">
+      <c r="K297" s="36">
         <v>178814.61851066299</v>
       </c>
-      <c r="L297" s="67">
+      <c r="L297" s="35">
         <v>53351.77086467755</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A298" s="5" t="s">
+      <c r="A298" s="70"/>
+      <c r="B298" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298" s="27">
+        <v>170666.99390453071</v>
+      </c>
+      <c r="D298" s="13">
+        <v>139156.72822134741</v>
+      </c>
+      <c r="E298" s="21">
+        <v>52887.332557327507</v>
+      </c>
+      <c r="F298" s="13">
+        <v>73605.672698937982</v>
+      </c>
+      <c r="G298" s="21">
+        <v>148275.39879635139</v>
+      </c>
+      <c r="H298" s="13">
+        <v>213829.80559140042</v>
+      </c>
+      <c r="I298" s="21">
+        <v>309986.63652111811</v>
+      </c>
+      <c r="J298" s="13">
+        <v>126308.18048367457</v>
+      </c>
+      <c r="K298" s="36">
+        <v>244053.19740944312</v>
+      </c>
+      <c r="L298" s="35">
+        <v>81660.9825215163</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A299" s="70"/>
+      <c r="B299" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C299" s="27">
+        <v>170728.89922753201</v>
+      </c>
+      <c r="D299" s="13">
+        <v>137144.19501152684</v>
+      </c>
+      <c r="E299" s="21">
+        <v>53130.71338245165</v>
+      </c>
+      <c r="F299" s="13">
+        <v>69342.498569297328</v>
+      </c>
+      <c r="G299" s="21">
+        <v>154142.9212453322</v>
+      </c>
+      <c r="H299" s="13">
+        <v>212774.64261718348</v>
+      </c>
+      <c r="I299" s="21">
+        <v>307908.36110530247</v>
+      </c>
+      <c r="J299" s="13">
+        <v>100962.6914700717</v>
+      </c>
+      <c r="K299" s="36">
+        <v>241096.81834977187</v>
+      </c>
+      <c r="L299" s="35">
+        <v>93950.760157535085</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="72"/>
+      <c r="B300" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C300" s="64">
+        <v>181789.77253500553</v>
+      </c>
+      <c r="D300" s="18">
+        <v>137076.57974938513</v>
+      </c>
+      <c r="E300" s="65">
+        <v>71743.438600632988</v>
+      </c>
+      <c r="F300" s="18">
+        <v>90572.780138039787</v>
+      </c>
+      <c r="G300" s="65">
+        <v>167966.53763291729</v>
+      </c>
+      <c r="H300" s="18">
+        <v>217553.71523694173</v>
+      </c>
+      <c r="I300" s="65">
+        <v>326636.64071338711</v>
+      </c>
+      <c r="J300" s="18">
+        <v>104105.91373662539</v>
+      </c>
+      <c r="K300" s="66">
+        <v>272474.58666398574</v>
+      </c>
+      <c r="L300" s="67">
+        <v>85303.445987499188</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A301" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A299" s="5" t="s">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A302" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A300" s="6" t="s">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A303" s="6" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A247:A258"/>
+    <mergeCell ref="A115:A126"/>
+    <mergeCell ref="A127:A138"/>
+    <mergeCell ref="A91:A102"/>
+    <mergeCell ref="A151:A162"/>
+    <mergeCell ref="A235:A246"/>
+    <mergeCell ref="A163:A174"/>
+    <mergeCell ref="A139:A150"/>
+    <mergeCell ref="A103:A114"/>
     <mergeCell ref="A283:A294"/>
-    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A295:A300"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A43:A54"/>
     <mergeCell ref="A55:A66"/>
@@ -12682,15 +12799,6 @@
     <mergeCell ref="A259:A270"/>
     <mergeCell ref="A79:A90"/>
     <mergeCell ref="C2:L2"/>
-    <mergeCell ref="A247:A258"/>
-    <mergeCell ref="A115:A126"/>
-    <mergeCell ref="A127:A138"/>
-    <mergeCell ref="A91:A102"/>
-    <mergeCell ref="A151:A162"/>
-    <mergeCell ref="A235:A246"/>
-    <mergeCell ref="A163:A174"/>
-    <mergeCell ref="A139:A150"/>
-    <mergeCell ref="A103:A114"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12793,7 +12901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
         <v>41</v>
       </c>
@@ -12801,7 +12909,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
         <v>42</v>
       </c>
@@ -12817,7 +12925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="54" t="s">
         <v>45</v>
       </c>
